--- a/site/Paycor-to-Active-Directory-Event-Based-Integration-Guide/headings.xlsx
+++ b/site/Paycor-to-Active-Directory-Event-Based-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,51 +661,51 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sensitive Fields</t>
+          <t>Correlation Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KSS80FGDS1WVZS7J1TGPBYTB</t>
+          <t>h_01KSSSWDQETSJRSXPKHEA7MXX9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS80FGDS1WVZS7J1TGPBYTB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSSSWDQETSJRSXPKHEA7MXX9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Log Settings</t>
+          <t>User Management</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KSS80FGD1TX9T91YX3BPTVDE</t>
+          <t>h_01KSSSWPFKAYDCPCRGM0B7795R</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS80FGD1TX9T91YX3BPTVDE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSSSWPFKAYDCPCRGM0B7795R</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Report Settings</t>
+          <t>Sensitive Fields</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KSS80FGDTYF1F68JGK59WQZ6</t>
+          <t>h_01KSS80FGDS1WVZS7J1TGPBYTB</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS80FGDTYF1F68JGK59WQZ6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS80FGDS1WVZS7J1TGPBYTB</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Log Settings</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -737,63 +737,63 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KSS80FGEKF2QTTY79MM7PSXR</t>
+          <t>h_01KSS80FGD1TX9T91YX3BPTVDE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS80FGEKF2QTTY79MM7PSXR</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS80FGD1TX9T91YX3BPTVDE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Notification Template Settings</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+          <t>h_01KSS80FGDTYF1F68JGK59WQZ6</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS80FGDTYF1F68JGK59WQZ6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Success Notifications</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KSSFMNSE65MXKD68KTE3XMXJ</t>
+          <t>h_01KSS80FGEKF2QTTY79MM7PSXR</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSSFMNSE65MXKD68KTE3XMXJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS80FGEKF2QTTY79MM7PSXR</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Failure Notifications</t>
+          <t>Notification Template Settings</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -803,19 +803,19 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01KSSFMNSE99F1XKSVGGNBQZTD</t>
+          <t>h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSSFMNSE99F1XKSVGGNBQZTD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KNRH0CCKYTWKSDADWQVSDY3Y</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Creation Mail To User</t>
+          <t>Success Notifications</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -825,19 +825,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>h_01KSSFK7YARC58MM7QN520FRTG</t>
+          <t>h_01KSSFMNSE65MXKD68KTE3XMXJ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSSFK7YARC58MM7QN520FRTG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSSFMNSE65MXKD68KTE3XMXJ</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Deactivation Mail to User</t>
+          <t>Failure Notifications</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -847,19 +847,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>h_01KSSFKAKA4PXWV2CRB2EVHG0T</t>
+          <t>h_01KSSFMNSE99F1XKSVGGNBQZTD</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSSFKAKA4PXWV2CRB2EVHG0T</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSSFMNSE99F1XKSVGGNBQZTD</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Notification Report Settings</t>
+          <t>Creation Mail To User</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -869,107 +869,107 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>h_01KSSFKPNQ9VF3311DJ3V1SVNG</t>
+          <t>h_01KSSFK7YARC58MM7QN520FRTG</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSSFKPNQ9VF3311DJ3V1SVNG</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSSFK7YARC58MM7QN520FRTG</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Log Insights</t>
+          <t>Deactivation Mail to User</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>h_01KSS80FGEVCWP8ST8GZWY0QG4</t>
+          <t>h_01KSSFKAKA4PXWV2CRB2EVHG0T</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS80FGEVCWP8ST8GZWY0QG4</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSSFKAKA4PXWV2CRB2EVHG0T</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Debug Mode</t>
+          <t>Notification Report Settings</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>h_01KSS80FGE1R6R8VM0M3PC11YB</t>
+          <t>h_01KSSFKPNQ9VF3311DJ3V1SVNG</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS80FGE1R6R8VM0M3PC11YB</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSSFKPNQ9VF3311DJ3V1SVNG</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Attribute Map</t>
+          <t>Log Insights</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KSS80ZRM3YXPK5SJ893ZWXWJ</t>
+          <t>h_01KSS80FGEVCWP8ST8GZWY0QG4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS80ZRM3YXPK5SJ893ZWXWJ</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS80FGEVCWP8ST8GZWY0QG4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Debug Mode</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KSS82D50AE1FB4SWS0MPH0ZS</t>
+          <t>h_01KSS80FGE1R6R8VM0M3PC11YB</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS82D50AE1FB4SWS0MPH0ZS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS80FGE1R6R8VM0M3PC11YB</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Attribute Map</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -979,19 +979,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KSS8146D67GQ7RX7TVRANY1Y</t>
+          <t>h_01KSS80ZRM3YXPK5SJ893ZWXWJ</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS8146D67GQ7RX7TVRANY1Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS80ZRM3YXPK5SJ893ZWXWJ</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1001,54 +1001,164 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KSS83WJ3T4AEHFACWC9CVJZ6</t>
+          <t>h_01KSS82D50AE1FB4SWS0MPH0ZS</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS83WJ3T4AEHFACWC9CVJZ6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS82D50AE1FB4SWS0MPH0ZS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Naming Policy</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KSSTT32Z1MADDAQA92RW4SAC</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSSTT32Z1MADDAQA92RW4SAC</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Naming Policy Settings</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KSSTW6AJYP0WPGSJQXG2Y4YS</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSSTW6AJYP0WPGSJQXG2Y4YS</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Password Policy</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KSSTT3301WARJ91NNT2V72WM</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSSTT3301WARJ91NNT2V72WM</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KSS8146D67GQ7RX7TVRANY1Y</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS8146D67GQ7RX7TVRANY1Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01KSS83WJ3T4AEHFACWC9CVJZ6</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS83WJ3T4AEHFACWC9CVJZ6</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/Paycor-to-Active-Directory-Event-Based-Integration-Guide/headings.xlsx
+++ b/site/Paycor-to-Active-Directory-Event-Based-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,120 +1045,230 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KSSTW6AJYP0WPGSJQXG2Y4YS</t>
+          <t>h_01KT0WP1CJYFNZ6NW5RSH3J9DF</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSSTW6AJYP0WPGSJQXG2Y4YS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KT0WP1CJYFNZ6NW5RSH3J9DF</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Password Policy</t>
+          <t>Generate UserPrincipalName (UPN)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KSSTT3301WARJ91NNT2V72WM</t>
+          <t>h_01KT0WR511R4BM8N8X1WQNTW9F</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSSTT3301WARJ91NNT2V72WM</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KT0WR511R4BM8N8X1WQNTW9F</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Generate sAMAccountName</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>h_01KSS8146D67GQ7RX7TVRANY1Y</t>
+          <t>h_01KT0WR512WNGHCHD0QR95NVP6</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS8146D67GQ7RX7TVRANY1Y</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KT0WR512WNGHCHD0QR95NVP6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Generate Email</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>h_01KSS83WJ3T4AEHFACWC9CVJZ6</t>
+          <t>h_01KT0WR512SM1MFQ6ZRTNF41ZP</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS83WJ3T4AEHFACWC9CVJZ6</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KT0WR512SM1MFQ6ZRTNF41ZP</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Generate Common Name (CN)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KT0WR512AXDP5WCCM83FHDWN</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KT0WR512AXDP5WCCM83FHDWN</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>Password Policy</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>h_01KSSTT3301WARJ91NNT2V72WM</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSSTT3301WARJ91NNT2V72WM</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Application Configuration</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>h_01KT0XPVBKXKABH13J0GQ5GGQY</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KT0XPVBKXKABH13J0GQ5GGQY</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Password Policy Configuration</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>h_01KT0XQ4D55PAG82QJQJPSR0PT</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KT0XQ4D55PAG82QJQJPSR0PT</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>h_01KSS83WJ3T4AEHFACWC9CVJZ6</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KSS83WJ3T4AEHFACWC9CVJZ6</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>

--- a/site/Paycor-to-Active-Directory-Event-Based-Integration-Guide/headings.xlsx
+++ b/site/Paycor-to-Active-Directory-Event-Based-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1211,7 +1211,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Event</t>
+          <t>Tables</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1233,42 +1233,64 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Additional Options</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>h_01KZNEV21BGBNDYV02MZZN4P6F</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KZNEV21BGBNDYV02MZZN4P6F</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>Additional Options</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
           <t>Update the Integration to the Latest Version</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Paycor-to-Active-Directory-Event-Based-Integration-Guide/#h_01KBFKZW49NWKGWCBPEP4C29R8</t>
         </is>
